--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-mailbox-mss.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -343,14 +343,16 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>boiteLettresMSS.typeBAL</t>
@@ -421,7 +423,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -437,7 +439,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-mailbox-mss.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-mailbox-mss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -343,16 +343,14 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
-- This extension allows to specify the type of mail used to contact the person.</t>
+    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
   </si>
   <si>
     <t>boiteLettresMSS.typeBAL</t>
@@ -423,7 +421,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -439,7 +437,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
